--- a/isolated_excel/Regression - Alpha and Beta.xlsx
+++ b/isolated_excel/Regression - Alpha and Beta.xlsx
@@ -475,13 +475,13 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>3.552270603645037</v>
+        <v>3.534642216788909</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>0.3882041321353366</v>
+        <v>0.3857634519698406</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>9.150522391674688</v>
+        <v>9.162719274570497</v>
       </c>
     </row>
     <row r="3">
@@ -491,13 +491,13 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>-0.02530998899887851</v>
+        <v>-0.02668390169468571</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>0.08305537019862617</v>
+        <v>0.08276917989976497</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>-0.3047363335850518</v>
+        <v>-0.32238934500741</v>
       </c>
     </row>
   </sheetData>
@@ -551,7 +551,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Jan 2017 to Jul 2026; 115 monthly observations</t>
+          <t>Jan 2017 to Aug 2026; 116 monthly observations</t>
         </is>
       </c>
     </row>

--- a/isolated_excel/Regression - Alpha and Beta.xlsx
+++ b/isolated_excel/Regression - Alpha and Beta.xlsx
@@ -475,13 +475,13 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>3.534642216788909</v>
+        <v>3.511429319936214</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>0.3857634519698406</v>
+        <v>0.3828516705792904</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>9.162719274570497</v>
+        <v>9.171774840692462</v>
       </c>
     </row>
     <row r="3">
@@ -491,13 +491,13 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>-0.02668390169468571</v>
+        <v>-0.02495282129216941</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>0.08276917989976497</v>
+        <v>0.08249578451452012</v>
       </c>
       <c r="D3" s="3" t="n">
-        <v>-0.32238934500741</v>
+        <v>-0.3024738953513129</v>
       </c>
     </row>
   </sheetData>
@@ -551,7 +551,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Jan 2017 to Aug 2026; 116 monthly observations</t>
+          <t>Jan 2017 to Sept 2026; 117 monthly observations</t>
         </is>
       </c>
     </row>
